--- a/lab-standards/Weaving-and-Finishing-Jute-lab-standard.xlsx
+++ b/lab-standards/Weaving-and-Finishing-Jute-lab-standard.xlsx
@@ -556,6 +556,10 @@
           <t>SICIP required space for 30 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -571,6 +575,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -640,7 +648,9 @@
       <c r="C16" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -662,7 +672,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -684,7 +696,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -706,7 +720,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>3</v>
       </c>
@@ -728,7 +744,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>3</v>
       </c>
@@ -750,7 +768,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -772,7 +792,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -794,7 +816,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -816,7 +840,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -838,7 +864,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -860,7 +888,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -882,7 +912,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -904,7 +936,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -926,7 +960,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -948,7 +984,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -970,7 +1008,9 @@
       <c r="C31" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>7</v>
       </c>
@@ -992,7 +1032,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
@@ -1014,7 +1056,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -1036,7 +1080,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>7</v>
       </c>
@@ -1058,7 +1104,9 @@
       <c r="C35" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>3</v>
       </c>
@@ -1080,7 +1128,9 @@
       <c r="C36" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>3</v>
       </c>
@@ -1102,7 +1152,9 @@
       <c r="C37" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>3</v>
       </c>
@@ -1124,7 +1176,9 @@
       <c r="C38" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>3</v>
       </c>
@@ -1146,7 +1200,9 @@
       <c r="C39" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>4</v>
       </c>
@@ -1168,7 +1224,9 @@
       <c r="C40" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>6</v>
       </c>
@@ -1190,7 +1248,9 @@
       <c r="C41" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>3</v>
       </c>
@@ -1212,7 +1272,9 @@
       <c r="C42" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="9" t="n"/>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="9" t="n">
         <v>5</v>
       </c>
@@ -1234,7 +1296,9 @@
       <c r="C43" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="D43" s="9" t="n"/>
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="9" t="n">
         <v>3</v>
       </c>
@@ -1256,7 +1320,9 @@
       <c r="C44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="9" t="n"/>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="9" t="n">
         <v>5</v>
       </c>
@@ -1278,7 +1344,9 @@
       <c r="C45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="9" t="n"/>
+      <c r="D45" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="9" t="n">
         <v>4</v>
       </c>
@@ -1300,7 +1368,9 @@
       <c r="C46" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="9" t="n"/>
+      <c r="D46" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="9" t="n">
         <v>3</v>
       </c>
@@ -1322,7 +1392,9 @@
       <c r="C47" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="9" t="n"/>
+      <c r="D47" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" s="9" t="n">
         <v>3</v>
       </c>
